--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N192_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N192_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.08886754583724</v>
+        <v>8.464440976198551</v>
       </c>
       <c r="D2" t="n">
-        <v>49.42207043846943</v>
+        <v>8.031086446251283</v>
       </c>
       <c r="E2" t="n">
-        <v>10.79687768075162</v>
+        <v>1.754492623122138</v>
       </c>
       <c r="F2" t="n">
-        <v>17.33445408769833</v>
+        <v>2.816848789250979</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.58892490730918</v>
+        <v>4.645700297437742</v>
       </c>
       <c r="D3" t="n">
-        <v>71.47047054416356</v>
+        <v>11.61395146342658</v>
       </c>
       <c r="E3" t="n">
-        <v>10.79687768075162</v>
+        <v>1.754492623122138</v>
       </c>
       <c r="F3" t="n">
-        <v>17.33445408769833</v>
+        <v>2.816848789250979</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.32249509070871</v>
+        <v>5.252405452240166</v>
       </c>
       <c r="D4" t="n">
-        <v>32.58567715355253</v>
+        <v>5.295172537452286</v>
       </c>
       <c r="E4" t="n">
-        <v>10.79687768075162</v>
+        <v>1.754492623122138</v>
       </c>
       <c r="F4" t="n">
-        <v>17.33445408769833</v>
+        <v>2.816848789250979</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.38953462547174</v>
+        <v>3.313299376639158</v>
       </c>
       <c r="D5" t="n">
-        <v>19.90417743072702</v>
+        <v>3.234428832493141</v>
       </c>
       <c r="E5" t="n">
-        <v>10.79687768075162</v>
+        <v>1.754492623122138</v>
       </c>
       <c r="F5" t="n">
-        <v>17.33445408769833</v>
+        <v>2.816848789250979</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.42032997223864</v>
+        <v>6.56830362048878</v>
       </c>
       <c r="D6" t="n">
-        <v>39.9528815544862</v>
+        <v>6.492343252604009</v>
       </c>
       <c r="E6" t="n">
-        <v>10.79687768075162</v>
+        <v>1.754492623122138</v>
       </c>
       <c r="F6" t="n">
-        <v>17.33445408769833</v>
+        <v>2.816848789250979</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
